--- a/09-School-Data-Export-data-cleaning/School_Data_Export_2023-2023_cleaned.xlsx
+++ b/09-School-Data-Export-data-cleaning/School_Data_Export_2023-2023_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R118"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,70 +439,65 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Primary Contact Person &amp; Details</t>
+          <t>Home Address</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Home Address</t>
+          <t>Tuition Fee Paid ($)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tuition Fee Paid ($)</t>
+          <t>Status / Remarks</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Status / Remarks</t>
+          <t>Parent Name</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Parent Name</t>
+          <t>Parent Phone</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Parent Phone</t>
+          <t>Parent Email</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Parent Email</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Teacher / Instructor</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Teacher / Instructor</t>
+          <t>Exam Date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Exam Date</t>
+          <t>Score / Grade</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Score / Grade</t>
+          <t>Attendance (%)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Attendance (%)</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
@@ -529,44 +524,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Contact: 555-743-3060 / elijah.davis@outlook.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t xml:space="preserve">765 Oak Ave </t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>5750</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557433060</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+15557433060</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>elijah.davis@outlook.com</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,44 +579,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Contact: 555-522-7115 / michael.flores@outlook.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t xml:space="preserve">590 Main St </t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="F3" t="n">
         <v>4200</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15555227115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+15555227115</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>michael.flores@outlook.com</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -649,44 +634,39 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Contact: 555-748-5243 / liam.garcia@gmail.com</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t xml:space="preserve">225 Pine St </t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
         <v>4500</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557485243</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+15557485243</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>liam.garcia@gmail.com</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -709,48 +689,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Father: Robert Smith | Ph: (555) 019-2831 | Email: rsmith@gmail.com</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t xml:space="preserve">123 Maple St </t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
         <v>5000</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Robert Smith</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Robert Smith</t>
+          <t>+15550192831</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+15550192831</t>
+          <t>rsmith@gmail.com</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>rsmith@gmail.com</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -773,60 +748,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Contact: 555-549-9224 / ethan.thomas@gmail.com</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t xml:space="preserve">453 Cedar Ln </t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>4200</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15555499224</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+15555499224</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>ethan.thomas@gmail.com</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mr. Mark Vance</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mr. Mark Vance</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
           <t>11/28/2023</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
           <t>History</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -849,44 +819,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>John Wright, john.wright@yahoo.com, 555-626-4362</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t xml:space="preserve">880 Main St </t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="F7" t="n">
         <v>5000</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>John Wright</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>John Wright</t>
+          <t>+15556264362</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+15556264362</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>john.wright@yahoo.com</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -909,44 +874,39 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mother: Susan Hall / 555-013-8899</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>258 Beech Dr</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
         <v>4200</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Susan Hall</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Susan Hall</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
           <t>+15550138899</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -969,48 +929,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mother: Mason Scott | Ph: 555-613-1608 | Email: mason.scott@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t xml:space="preserve">148 Main St </t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="F9" t="n">
         <v>5750</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Mason Scott</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mason Scott</t>
+          <t>+15556131608</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+15556131608</t>
+          <t>mason.scott@yahoo.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>mason.scott@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1033,48 +988,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Parent: John Wright | Ph: 555-539-6250 | Email: john.wright@gmail.com</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t xml:space="preserve">463 Main St </t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
         <v>4200</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>John Wright</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>John Wright</t>
+          <t>+15555396250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+15555396250</t>
+          <t>john.wright@gmail.com</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>john.wright@gmail.com</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1097,48 +1047,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mother: Karen Johnson | 555-016-7788 | k.johnson@domain.org</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>753 Spruce Ct</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="F11" t="n">
         <v>4200</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Karen Johnson</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Karen Johnson</t>
+          <t>+15550167788</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+15550167788</t>
+          <t>k.johnson@domain.org</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>k.johnson@domain.org</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1161,42 +1106,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sebastian Anderson (Parent) - 555-300-3237</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t xml:space="preserve">301 Main St </t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Sebastian Anderson</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sebastian Anderson</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
           <t>+15553003237</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1219,44 +1159,39 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Father: Mark Harris | ph: 555-012-9988</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>147 Cypress Way</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="F13" t="n">
         <v>5000</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Mark Harris</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mark Harris</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>+15550129988</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1279,44 +1214,39 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jack Johnson, jack.johnson@outlook.com, 555-925-3104</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t xml:space="preserve">398 Pine St </t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="F14" t="n">
         <v>4500</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Jack Johnson</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jack Johnson</t>
+          <t>+15559253104</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+15559253104</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
           <t>jack.johnson@outlook.com</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1339,44 +1269,39 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aiden Ramirez, aiden.ramirez@gmail.com, 555-260-2676</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t xml:space="preserve">786 Maple Rd </t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="F15" t="n">
         <v>5000</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Aiden Ramirez</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aiden Ramirez</t>
+          <t>+15552602676</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+15552602676</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
           <t>aiden.ramirez@gmail.com</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1399,44 +1324,39 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mother: Patricia Lewis (555) 014-3322</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>147 Willow Ave</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="F16" t="n">
         <v>4500</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Patricia Lewis</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Patricia Lewis</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>+15550143322</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1459,62 +1379,57 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Father: David Lee / mob: 555-017-8811</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>654 Elm St</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
         <v>4800</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>David Lee</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>David Lee</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
           <t>+15550178811</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Prof. Sarah Jenkins</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Prof. Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
           <t>09/20/2023</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="N17" t="n">
         <v>62</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
         <is>
           <t>301</t>
         </is>
@@ -1541,44 +1456,39 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Contact: 555-880-3765 / william.white@gmail.com</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
           <t xml:space="preserve">701 Pine St </t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="F18" t="n">
         <v>3750</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15558803765</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+15558803765</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
           <t>william.white@gmail.com</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1601,44 +1511,39 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jacob Wright (Guardian) - 555-256-9158</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
           <t xml:space="preserve">401 Oak Ave </t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="F19" t="n">
         <v>3750</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Jacob Wright</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jacob Wright</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
           <t>+15552569158</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1661,66 +1566,61 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mother: Theodore Rodriguez | Ph: 555-788-7553 | Email: theodore.rodriguez@gmail.com</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t xml:space="preserve">266 Oak Ave </t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="F20" t="n">
         <v>4500</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Theodore Rodriguez</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Theodore Rodriguez</t>
+          <t>+15557887553</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+15557887553</t>
+          <t>theodore.rodriguez@gmail.com</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>theodore.rodriguez@gmail.com</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Prof. Sarah Jenkins</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Prof. Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
           <t>10/02/2023</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="N20" t="n">
         <v>62</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>86.0%</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>86.0%</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1743,44 +1643,39 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>William Thompson, william.thompson@outlook.com, 555-717-1065</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t xml:space="preserve">118 Maple Rd </t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="F21" t="n">
         <v>4500</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>William Thompson</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>William Thompson</t>
+          <t>+15557171065</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+15557171065</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
           <t>william.thompson@outlook.com</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1803,44 +1698,39 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Henry Clark (Parent) - 555-990-8537</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t xml:space="preserve">670 Maple Rd </t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="F22" t="n">
         <v>4500</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Henry Clark</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Henry Clark</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
           <t>+15559908537</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1863,48 +1753,43 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Parent: Hudson Hill | Ph: 555-369-7741 | Email: hudson.hill@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
           <t xml:space="preserve">283 Oak Ave </t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="F23" t="n">
         <v>5750</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Hudson Hill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hudson Hill</t>
+          <t>+15553697741</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+15553697741</t>
+          <t>hudson.hill@yahoo.com</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hudson.hill@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1927,58 +1812,57 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Henry Thomas (Mother) - 555-841-8820</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t xml:space="preserve">211 Maple Rd </t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
         <v>5000</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Henry Thomas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Henry Thomas</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
           <t>+15558418820</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Prof. Sarah Jenkins</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Prof. Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
           <t>10/05/2023</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="N24" t="n">
         <v>58</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2001,48 +1885,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mother - Sarah Watson - 555-014-9922 - swatson@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t xml:space="preserve">456 Oak Ave Apt 2B </t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="F25" t="n">
         <v>4500</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Sarah Watson</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sarah Watson</t>
+          <t>+15550149922</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>+15550149922</t>
+          <t>swatson@yahoo.com</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>swatson@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2065,62 +1944,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Father: Steven Clark - 555-018-1122</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
           <t>369 Poplar Rd</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="F26" t="n">
         <v>5000</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Steven Clark</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Steven Clark</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
           <t>+15550181122</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Dr. A. Thorne</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Dr. A. Thorne</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
           <t>11/18/2023</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="N26" t="n">
         <v>89</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>92.0%</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>History</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -2147,44 +2021,39 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Michael Martin (Father) - 555-885-2172</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t xml:space="preserve">890 Cedar Ln </t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="F27" t="n">
         <v>4800</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Michael Martin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Michael Martin</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
           <t>+15558852172</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2207,44 +2076,39 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mason Thompson (Mother) - 555-645-6886</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
           <t xml:space="preserve">783 Maple Rd </t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="F28" t="n">
         <v>4500</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Mason Thompson</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mason Thompson</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
           <t>+15556456886</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2267,44 +2131,39 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mother: Nancy Scott / 555-016-2211</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>159 Sycamore St</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="F29" t="n">
         <v>4200</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Nancy Scott</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Nancy Scott</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
           <t>+15550162211</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2327,44 +2186,39 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Contact: 555-242-5145 / logan.nguyen@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
           <t xml:space="preserve">775 Main St </t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="F30" t="n">
         <v>3750</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15552425145</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+15552425145</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
           <t>logan.nguyen@yahoo.com</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2387,46 +2241,41 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mother: Hudson Perez | Ph: 555-664-3656 | Email: hudson.perez@gmail.com</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
           <t xml:space="preserve">339 Oak Ave </t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Hudson Perez</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hudson Perez</t>
+          <t>+15556643656</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+15556643656</t>
+          <t>hudson.perez@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hudson.perez@gmail.com</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2449,44 +2298,39 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contact: 555-339-7438 / luke.scott@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
           <t xml:space="preserve">516 Oak Ave </t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="F32" t="n">
         <v>4800</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15553397438</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+15553397438</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
           <t>luke.scott@yahoo.com</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2509,44 +2353,39 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mother: Jessica Young | jyoung@org.net</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
           <t>852 Fir Rd</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="F33" t="n">
         <v>4500</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Enrolled</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
           <t>Jessica Young</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>jyoung@org.net</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>jyoung@org.net</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2569,44 +2408,39 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Henry Gonzalez (Mother) - 555-602-6649</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
           <t xml:space="preserve">347 Cedar Ln </t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="F34" t="n">
         <v>5000</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Henry Gonzalez</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Henry Gonzalez</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
           <t>+15556026649</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2629,48 +2463,43 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guardian: Alexander Hill | Ph: 555-135-1516 | Email: alexander.hill@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
           <t xml:space="preserve">465 Maple Rd </t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="F35" t="n">
         <v>5000</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Alexander Hill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Alexander Hill</t>
+          <t>+15551351516</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+15551351516</t>
+          <t>alexander.hill@hotmail.com</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>alexander.hill@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2693,42 +2522,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Father: Richard Walker / rwalker@corp.com</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
           <t>369 Alder St</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Enrolled</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
           <t>Richard Walker</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>rwalker@corp.com</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>rwalker@corp.com</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2751,48 +2575,43 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Father: Gabriel Allen | Ph: 555-428-4117 | Email: gabriel.allen@outlook.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t xml:space="preserve">686 Main St </t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="F37" t="n">
         <v>4500</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Gabriel Allen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Gabriel Allen</t>
+          <t>+15554284117</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+15554284117</t>
+          <t>gabriel.allen@outlook.com</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>gabriel.allen@outlook.com</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2815,44 +2634,39 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oliver Garcia, oliver.garcia@hotmail.com, 555-567-5597</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
           <t xml:space="preserve">987 Maple Rd </t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="F38" t="n">
         <v>4500</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Oliver Garcia</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Oliver Garcia</t>
+          <t>+15555675597</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+15555675597</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
           <t>oliver.garcia@hotmail.com</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2875,48 +2689,43 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guardian: Noah Miller | Ph: 555-325-4750 | Email: noah.miller@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
           <t xml:space="preserve">480 Maple Rd </t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="F39" t="n">
         <v>5000</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Noah Miller</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Noah Miller</t>
+          <t>+15553254750</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+15553254750</t>
+          <t>noah.miller@hotmail.com</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>noah.miller@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2939,44 +2748,39 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mateo Rodriguez (Mother) - 555-574-1601</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
           <t xml:space="preserve">435 Main St </t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="F40" t="n">
         <v>5000</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Mateo Rodriguez</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mateo Rodriguez</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
           <t>+15555741601</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2999,44 +2803,39 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Contact: 555-134-5809 / david.sanchez@gmail.com</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
           <t xml:space="preserve">967 Pine St </t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="F41" t="n">
         <v>4500</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15551345809</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+15551345809</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
           <t>david.sanchez@gmail.com</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3059,44 +2858,39 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Levi Thompson (Parent) - 555-324-5588</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
           <t xml:space="preserve">997 Maple Rd </t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="F42" t="n">
         <v>5000</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Levi Thompson</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Levi Thompson</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
           <t>+15553245588</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3119,44 +2913,39 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>James White, james.white@hotmail.com, 555-326-9055</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
           <t xml:space="preserve">475 Maple Rd </t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="F43" t="n">
         <v>5750</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>James White</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>James White</t>
+          <t>+15553269055</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+15553269055</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
           <t>james.white@hotmail.com</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3179,44 +2968,39 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grayson Clark (Guardian) - 555-719-5906</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
           <t xml:space="preserve">633 Maple Rd </t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="F44" t="n">
         <v>5750</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Grayson Clark</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Grayson Clark</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
           <t>+15557195906</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3239,44 +3023,39 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Contact: 555-796-4201 / joseph.flores@gmail.com</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
           <t xml:space="preserve">178 Pine St </t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="F45" t="n">
         <v>5750</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557964201</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>+15557964201</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
           <t>joseph.flores@gmail.com</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3299,48 +3078,43 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Father: Ethan Garcia | Ph: 555-245-4115 | Email: ethan.garcia@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
           <t xml:space="preserve">544 Oak Ave </t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="F46" t="n">
         <v>5750</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Ethan Garcia</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Ethan Garcia</t>
+          <t>+15552454115</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>+15552454115</t>
+          <t>ethan.garcia@hotmail.com</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>ethan.garcia@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3363,44 +3137,39 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Contact: 555-705-8898 / michael.perez@gmail.com</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
           <t xml:space="preserve">537 Cedar Ln </t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="F47" t="n">
         <v>4800</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557058898</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+15557058898</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
           <t>michael.perez@gmail.com</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3423,42 +3192,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Contact: 555-583-4219 / samuel.sanchez@outlook.com</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
           <t xml:space="preserve">448 Oak Ave </t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15555834219</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>+15555834219</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
           <t>samuel.sanchez@outlook.com</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3481,44 +3245,39 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mother: Rosa Garcia / 555-019-0011</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
           <t>951 Redwood Dr</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="F49" t="n">
         <v>4500</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Rosa Garcia</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Rosa Garcia</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
           <t>+15550190011</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3541,44 +3300,39 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Joseph Clark (Mother) - 555-514-2428</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
           <t xml:space="preserve">283 Main St </t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="F50" t="n">
         <v>4500</v>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Joseph Clark</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Joseph Clark</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
           <t>+15555142428</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3601,44 +3355,39 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Contact: 555-900-7810 / hudson.allen@outlook.com</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
           <t xml:space="preserve">169 Main St </t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="F51" t="n">
         <v>4500</v>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15559007810</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+15559007810</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
           <t>hudson.allen@outlook.com</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3661,44 +3410,39 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wyatt Scott (Mother) - 555-828-2874</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
           <t xml:space="preserve">180 Main St </t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="F52" t="n">
         <v>5000</v>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Wyatt Scott</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Wyatt Scott</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
           <t>+15558282874</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3721,44 +3465,39 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Contact: 555-852-1826 / lincoln.king@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
           <t xml:space="preserve">866 Main St </t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="F53" t="n">
         <v>5750</v>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15558521826</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+15558521826</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
           <t>lincoln.king@yahoo.com</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3781,44 +3520,39 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Elijah Martin (Mother) - 555-721-4747</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
           <t xml:space="preserve">164 Pine St </t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="F54" t="n">
         <v>4500</v>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Elijah Martin</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Elijah Martin</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
           <t>+15557214747</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3841,48 +3575,43 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Parent: Aiden Sanchez | Ph: 555-106-9439 | Email: aiden.sanchez@outlook.com</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
           <t xml:space="preserve">579 Oak Ave </t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="F55" t="n">
         <v>5750</v>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Aiden Sanchez</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Aiden Sanchez</t>
+          <t>+15551069439</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+15551069439</t>
+          <t>aiden.sanchez@outlook.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>aiden.sanchez@outlook.com</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3905,44 +3634,39 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Contact: 555-480-4322 / levi.gonzalez@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
           <t xml:space="preserve">564 Pine St </t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="F56" t="n">
         <v>4500</v>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15554804322</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>+15554804322</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
           <t>levi.gonzalez@hotmail.com</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3965,44 +3689,39 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Uncle: Peter Wilson - 555.015.6677</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
           <t>852 Ash Rd</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="F57" t="n">
         <v>3750</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Peter Wilson</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Peter Wilson</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
           <t>+15550156677</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Uncle</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4025,44 +3744,39 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Contact: 555-411-4684 / james.davis@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
           <t xml:space="preserve">606 Main St </t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="F58" t="n">
         <v>4800</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15554114684</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>+15554114684</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
           <t>james.davis@hotmail.com</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4085,44 +3799,39 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hudson Ramirez (Mother) - 555-565-6602</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
           <t xml:space="preserve">645 Pine St </t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="F59" t="n">
         <v>4500</v>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Hudson Ramirez</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hudson Ramirez</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
           <t>+15555656602</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4145,44 +3854,39 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Isaac Smith (Parent) - 555-561-3293</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
           <t xml:space="preserve">331 Cedar Ln </t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="F60" t="n">
         <v>5750</v>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Isaac Smith</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Isaac Smith</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
           <t>+15555613293</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4205,44 +3909,39 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mateo Lopez, mateo.lopez@hotmail.com, 555-398-4205</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
           <t xml:space="preserve">250 Oak Ave </t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="F61" t="n">
         <v>3750</v>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Mateo Lopez</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mateo Lopez</t>
+          <t>+15553984205</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>+15553984205</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
           <t>mateo.lopez@hotmail.com</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4265,44 +3964,39 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jacob Nguyen, jacob.nguyen@gmail.com, 555-409-6160</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
           <t xml:space="preserve">349 Cedar Ln </t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="F62" t="n">
         <v>4200</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Jacob Nguyen</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Jacob Nguyen</t>
+          <t>+15554096160</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>+15554096160</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
           <t>jacob.nguyen@gmail.com</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4325,62 +4019,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Contact: 555-773-9694 / luke.allen@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
           <t xml:space="preserve">520 Cedar Ln </t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="F63" t="n">
         <v>4500</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557739694</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>+15557739694</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
           <t>luke.allen@yahoo.com</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Mrs. Elena Rostova</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Mrs. Elena Rostova</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
           <t>12/23/2023</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="N63" t="n">
         <v>94</v>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4403,48 +4092,43 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Father: Levi Scott | Ph: 555-701-5349 | Email: levi.scott@gmail.com</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
           <t xml:space="preserve">488 Main St </t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="F64" t="n">
         <v>4500</v>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Levi Scott</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Levi Scott</t>
+          <t>+15557015349</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>+15557015349</t>
+          <t>levi.scott@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>levi.scott@gmail.com</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4467,58 +4151,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hudson Anderson (Parent) - 555-365-2691</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
           <t xml:space="preserve">624 Pine St </t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="F65" t="n">
         <v>5000</v>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Hudson Anderson</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hudson Anderson</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
           <t>+15553652691</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Mr. Mark Vance</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Mr. Mark Vance</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
           <t>10/15/2023</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="N65" t="n">
         <v>59</v>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4541,44 +4224,39 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Contact: 555-446-4767 / wyatt.nguyen@outlook.com</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
           <t xml:space="preserve">609 Pine St </t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="F66" t="n">
         <v>5000</v>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15554464767</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>+15554464767</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
           <t>wyatt.nguyen@outlook.com</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4601,62 +4279,61 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guardian: Theodore Rodriguez | Ph: 555-575-5211 | Email: theodore.rodriguez@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
           <t xml:space="preserve">908 Cedar Ln </t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="F67" t="n">
         <v>4800</v>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Theodore Rodriguez</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Theodore Rodriguez</t>
+          <t>+15555755211</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>+15555755211</t>
+          <t>theodore.rodriguez@hotmail.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>theodore.rodriguez@hotmail.com</t>
+          <t>Guardian</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Prof. Sarah Jenkins</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Prof. Sarah Jenkins</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
           <t>10/05/2023</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="N67" t="n">
         <v>83</v>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -4683,48 +4360,43 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Father: Hudson Sanchez | Ph: 555-464-5808 | Email: hudson.sanchez@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
           <t xml:space="preserve">643 Main St </t>
         </is>
       </c>
-      <c r="G68" t="n">
+      <c r="F68" t="n">
         <v>4500</v>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Hudson Sanchez</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hudson Sanchez</t>
+          <t>+15554645808</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>+15554645808</t>
+          <t>hudson.sanchez@yahoo.com</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hudson.sanchez@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4747,44 +4419,39 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Contact: 555-994-1263 / john.allen@outlook.com</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
           <t xml:space="preserve">609 Cedar Ln </t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="F69" t="n">
         <v>5750</v>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15559941263</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>+15559941263</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
           <t>john.allen@outlook.com</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4807,44 +4474,39 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sebastian Gonzalez (Guardian) - 555-255-8338</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
           <t xml:space="preserve">670 Pine St </t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="F70" t="n">
         <v>4500</v>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Sebastian Gonzalez</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sebastian Gonzalez</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
           <t>+15552558338</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4867,44 +4529,39 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grayson Jackson, grayson.jackson@hotmail.com, 555-795-2006</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
           <t xml:space="preserve">486 Cedar Ln </t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="F71" t="n">
         <v>5750</v>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Grayson Jackson</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Grayson Jackson</t>
+          <t>+15557952006</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>+15557952006</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
           <t>grayson.jackson@hotmail.com</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4927,44 +4584,39 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Contact: 555-378-8319 / noah.white@outlook.com</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
           <t xml:space="preserve">504 Pine St </t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="F72" t="n">
         <v>5750</v>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15553788319</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>+15553788319</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
           <t>noah.white@outlook.com</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4987,48 +4639,43 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guardian: Wyatt Johnson | Ph: 555-956-9700 | Email: wyatt.johnson@gmail.com</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
           <t xml:space="preserve">980 Cedar Ln </t>
         </is>
       </c>
-      <c r="G73" t="n">
+      <c r="F73" t="n">
         <v>5000</v>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Wyatt Johnson</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Wyatt Johnson</t>
+          <t>+15559569700</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>+15559569700</t>
+          <t>wyatt.johnson@gmail.com</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>wyatt.johnson@gmail.com</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5051,62 +4698,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>James Lee, james.lee@yahoo.com, 555-803-3370</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
           <t xml:space="preserve">863 Cedar Ln </t>
         </is>
       </c>
-      <c r="G74" t="n">
+      <c r="F74" t="n">
         <v>3750</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>James Lee</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>James Lee</t>
+          <t>+15558033370</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>+15558033370</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
           <t>james.lee@yahoo.com</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Dr. Aris Thorne</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Dr. Aris Thorne</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
           <t>10/01/2023</t>
         </is>
       </c>
-      <c r="O74" t="n">
+      <c r="N74" t="n">
         <v>97</v>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>94.0%</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>94.0%</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5129,44 +4771,39 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>William Williams (Mother) - 555-227-4843</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
           <t xml:space="preserve">664 Pine St </t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="F75" t="n">
         <v>4200</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>William Williams</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>William Williams</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
           <t>+15552274843</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5189,44 +4826,39 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Father: Charles Allen - 555.017.4433</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
           <t>741 Chestnut St</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="F76" t="n">
         <v>5000</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Charles Allen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Charles Allen</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
           <t>+15550174433</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5249,44 +4881,39 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Contact: 555-284-4042 / joseph.hill@gmail.com</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
           <t xml:space="preserve">502 Main St </t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="F77" t="n">
         <v>5750</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15552844042</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>+15552844042</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
           <t>joseph.hill@gmail.com</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5309,62 +4936,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grayson Johnson (Father) - 555-862-8161</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
           <t xml:space="preserve">251 Cedar Ln </t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="F78" t="n">
         <v>4500</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Grayson Johnson</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Grayson Johnson</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
           <t>+15558628161</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Dr. Aris Thorne</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Dr. Aris Thorne</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
           <t>09/21/2023</t>
         </is>
       </c>
-      <c r="O78" t="n">
+      <c r="N78" t="n">
         <v>94</v>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
         <is>
           <t>201</t>
         </is>
@@ -5391,44 +5013,39 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jack Lopez (Father) - 555-973-5159</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
           <t xml:space="preserve">784 Oak Ave </t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="F79" t="n">
         <v>4200</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Jack Lopez</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Jack Lopez</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
           <t>+15559735159</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5451,44 +5068,39 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>William Nguyen (Mother) - 555-896-1083</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
           <t xml:space="preserve">823 Maple Rd </t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="F80" t="n">
         <v>4800</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>William Nguyen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>William Nguyen</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
           <t>+15558961083</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5511,48 +5123,43 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Father: Levi Allen | Ph: 555-260-6325 | Email: levi.allen@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
           <t xml:space="preserve">639 Pine St </t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="F81" t="n">
         <v>4500</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Levi Allen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Levi Allen</t>
+          <t>+15552606325</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>+15552606325</t>
+          <t>levi.allen@hotmail.com</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>levi.allen@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5575,62 +5182,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Luke Hill, luke.hill@outlook.com, 555-392-3648</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
           <t xml:space="preserve">776 Maple Rd </t>
         </is>
       </c>
-      <c r="G82" t="n">
+      <c r="F82" t="n">
         <v>3750</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Luke Hill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Luke Hill</t>
+          <t>+15553923648</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>+15553923648</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
           <t>luke.hill@outlook.com</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Dr. A. Thorne</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Dr. A. Thorne</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
           <t>09/25/2023</t>
         </is>
       </c>
-      <c r="O82" t="n">
+      <c r="N82" t="n">
         <v>90</v>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>89.0%</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>89.0%</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5653,44 +5255,39 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Elijah Jones (Mother) - 555-684-3958</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
           <t xml:space="preserve">458 Maple Rd </t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="F83" t="n">
         <v>5000</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Elijah Jones</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Elijah Jones</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
           <t>+15556843958</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5713,44 +5310,39 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Levi Nguyen, levi.nguyen@gmail.com, 555-556-1756</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
           <t xml:space="preserve">608 Maple Rd </t>
         </is>
       </c>
-      <c r="G84" t="n">
+      <c r="F84" t="n">
         <v>5000</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Levi Nguyen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Levi Nguyen</t>
+          <t>+15555561756</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>+15555561756</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
           <t>levi.nguyen@gmail.com</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5773,66 +5365,61 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mother: Samuel Torres | Ph: 555-577-7850 | Email: samuel.torres@gmail.com</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
           <t xml:space="preserve">308 Main St </t>
         </is>
       </c>
-      <c r="G85" t="n">
+      <c r="F85" t="n">
         <v>5750</v>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Samuel Torres</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Samuel Torres</t>
+          <t>+15555777850</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>+15555777850</t>
+          <t>samuel.torres@gmail.com</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>samuel.torres@gmail.com</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Mrs. Elena Rostova</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Mrs. Elena Rostova</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
           <t>12/18/2023</t>
         </is>
       </c>
-      <c r="O85" t="n">
+      <c r="N85" t="n">
         <v>56</v>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
         <is>
           <t>301</t>
         </is>
@@ -5859,42 +5446,37 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Contact: 555-839-3442 / john.garcia@gmail.com</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
           <t xml:space="preserve">419 Main St </t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15558393442</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>+15558393442</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
           <t>john.garcia@gmail.com</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5917,44 +5499,39 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Luke Harris (Mother) - 555-752-3611</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
           <t xml:space="preserve">965 Maple Rd </t>
         </is>
       </c>
-      <c r="G87" t="n">
+      <c r="F87" t="n">
         <v>5750</v>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Luke Harris</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Luke Harris</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
           <t>+15557523611</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5977,62 +5554,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Father: Paul King | 555-011-5544</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
           <t>963 Hickory Ave</t>
         </is>
       </c>
-      <c r="G88" t="n">
+      <c r="F88" t="n">
         <v>5000</v>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Paul King</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Paul King</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
           <t>+15550115544</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Dr. A. Thorne</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Dr. A. Thorne</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
           <t>09/26/2023</t>
         </is>
       </c>
-      <c r="O88" t="n">
+      <c r="N88" t="n">
         <v>74</v>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>84.0%</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>84.0%</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6055,44 +5627,39 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mason Young, mason.young@outlook.com, 555-525-6293</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
           <t xml:space="preserve">577 Cedar Ln </t>
         </is>
       </c>
-      <c r="G89" t="n">
+      <c r="F89" t="n">
         <v>4500</v>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Mason Young</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Mason Young</t>
+          <t>+15555256293</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>+15555256293</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
           <t>mason.young@outlook.com</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6115,44 +5682,39 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>William Brown, william.brown@gmail.com, 555-891-7616</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
           <t xml:space="preserve">836 Maple Rd </t>
         </is>
       </c>
-      <c r="G90" t="n">
+      <c r="F90" t="n">
         <v>4200</v>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>William Brown</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>William Brown</t>
+          <t>+15558917616</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>+15558917616</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
           <t>william.brown@gmail.com</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6175,44 +5737,39 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>William Harris (Mother) - 555-313-8684</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
           <t xml:space="preserve">468 Cedar Ln </t>
         </is>
       </c>
-      <c r="G91" t="n">
+      <c r="F91" t="n">
         <v>5000</v>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>William Harris</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>William Harris</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
           <t>+15553138684</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6235,48 +5792,43 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guardian: Matthew Robinson | Ph: 555-239-4937 | Email: matthew.robinson@gmail.com</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
           <t xml:space="preserve">178 Oak Ave </t>
         </is>
       </c>
-      <c r="G92" t="n">
+      <c r="F92" t="n">
         <v>5750</v>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Matthew Robinson</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Matthew Robinson</t>
+          <t>+15552394937</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>+15552394937</t>
+          <t>matthew.robinson@gmail.com</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>matthew.robinson@gmail.com</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6299,44 +5851,39 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wyatt Scott (Parent) - 555-149-3170</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
           <t xml:space="preserve">168 Maple Rd </t>
         </is>
       </c>
-      <c r="G93" t="n">
+      <c r="F93" t="n">
         <v>4500</v>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Wyatt Scott</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Wyatt Scott</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
           <t>+15551493170</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6359,44 +5906,39 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mother: Jennifer White | jwhite@net.com</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
           <t>258 Magnolia St</t>
         </is>
       </c>
-      <c r="G94" t="n">
+      <c r="F94" t="n">
         <v>4200</v>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Enrolled</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
           <t>Jennifer White</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>jwhite@net.com</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>jwhite@net.com</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6419,44 +5961,39 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guardian: James Brown / 555.018.3344</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
           <t xml:space="preserve">789 Pine Rd </t>
         </is>
       </c>
-      <c r="G95" t="n">
+      <c r="F95" t="n">
         <v>5750</v>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>James Brown</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>James Brown</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
           <t>+15550183344</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6479,44 +6016,39 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jack Wilson (Parent) - 555-108-7984</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
           <t xml:space="preserve">944 Oak Ave </t>
         </is>
       </c>
-      <c r="G96" t="n">
+      <c r="F96" t="n">
         <v>3750</v>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Jack Wilson</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Jack Wilson</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
           <t>+15551087984</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6539,48 +6071,43 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guardian: Noah Nguyen | Ph: 555-953-7809 | Email: noah.nguyen@gmail.com</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
           <t xml:space="preserve">220 Oak Ave </t>
         </is>
       </c>
-      <c r="G97" t="n">
+      <c r="F97" t="n">
         <v>4500</v>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Noah Nguyen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Noah Nguyen</t>
+          <t>+15559537809</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>+15559537809</t>
+          <t>noah.nguyen@gmail.com</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>noah.nguyen@gmail.com</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6603,48 +6130,43 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mother: Laura Taylor / email: ltaylor@service.com / tel: 555-011-2233</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
           <t>987 Birch Rd</t>
         </is>
       </c>
-      <c r="G98" t="n">
+      <c r="F98" t="n">
         <v>4500</v>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Laura Taylor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Laura Taylor</t>
+          <t>+15550112233</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>+15550112233</t>
+          <t>ltaylor@service.com</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ltaylor@service.com</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6667,48 +6189,43 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mother: Noah Clark | Ph: 555-681-9857 | Email: noah.clark@outlook.com</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
           <t xml:space="preserve">996 Pine St </t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="F99" t="n">
         <v>4500</v>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Noah Clark</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Noah Clark</t>
+          <t>+15556819857</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>+15556819857</t>
+          <t>noah.clark@outlook.com</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>noah.clark@outlook.com</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6731,48 +6248,43 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Father: Logan Davis | Ph: 555-498-2052 | Email: logan.davis@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
           <t xml:space="preserve">691 Cedar Ln </t>
         </is>
       </c>
-      <c r="G100" t="n">
+      <c r="F100" t="n">
         <v>4500</v>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Logan Davis</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Logan Davis</t>
+          <t>+15554982052</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>+15554982052</t>
+          <t>logan.davis@yahoo.com</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>logan.davis@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6795,48 +6307,43 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guardian: Levi Garcia | Ph: 555-153-6895 | Email: levi.garcia@outlook.com</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
           <t xml:space="preserve">246 Main St </t>
         </is>
       </c>
-      <c r="G101" t="n">
+      <c r="F101" t="n">
         <v>4200</v>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Levi Garcia</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Levi Garcia</t>
+          <t>+15551536895</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>+15551536895</t>
+          <t>levi.garcia@outlook.com</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>levi.garcia@outlook.com</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6859,44 +6366,39 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Contact: 555-743-9962 / noah.rodriguez@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
           <t xml:space="preserve">492 Cedar Ln </t>
         </is>
       </c>
-      <c r="G102" t="n">
+      <c r="F102" t="n">
         <v>4500</v>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15557439962</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>+15557439962</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
           <t>noah.rodriguez@hotmail.com</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6919,44 +6421,39 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Henry White (Mother) - 555-896-3728</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
           <t xml:space="preserve">223 Oak Ave </t>
         </is>
       </c>
-      <c r="G103" t="n">
+      <c r="F103" t="n">
         <v>4500</v>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Henry White</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Henry White</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
           <t>+15558963728</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6979,42 +6476,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Matthew Brown (Parent) - 555-512-7938</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
           <t xml:space="preserve">810 Maple Rd </t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Matthew Brown</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Matthew Brown</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
           <t>+15555127938</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7037,48 +6529,43 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Father: Liam Harris | Ph: 555-886-5086 | Email: liam.harris@gmail.com</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
           <t xml:space="preserve">172 Main St </t>
         </is>
       </c>
-      <c r="G105" t="n">
+      <c r="F105" t="n">
         <v>4500</v>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Liam Harris</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Liam Harris</t>
+          <t>+15558865086</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>+15558865086</t>
+          <t>liam.harris@gmail.com</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>liam.harris@gmail.com</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7101,48 +6588,43 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Guardian: Sebastian Lewis | Ph: 555-973-7526 | Email: sebastian.lewis@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
           <t xml:space="preserve">405 Oak Ave </t>
         </is>
       </c>
-      <c r="G106" t="n">
+      <c r="F106" t="n">
         <v>4800</v>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Sebastian Lewis</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Sebastian Lewis</t>
+          <t>+15559737526</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>+15559737526</t>
+          <t>sebastian.lewis@yahoo.com</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>sebastian.lewis@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7165,48 +6647,43 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Guardian: Logan Thompson | Ph: 555-653-8419 | Email: logan.thompson@outlook.com</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
           <t xml:space="preserve">662 Main St </t>
         </is>
       </c>
-      <c r="G107" t="n">
+      <c r="F107" t="n">
         <v>3750</v>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Logan Thompson</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Logan Thompson</t>
+          <t>+15556538419</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>+15556538419</t>
+          <t>logan.thompson@outlook.com</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>logan.thompson@outlook.com</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
           <t>Guardian</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7229,66 +6706,61 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Parent: Luke King | Ph: 555-700-3932 | Email: luke.king@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
           <t xml:space="preserve">659 Maple Rd </t>
         </is>
       </c>
-      <c r="G108" t="n">
+      <c r="F108" t="n">
         <v>4500</v>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Luke King</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Luke King</t>
+          <t>+15557003932</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>+15557003932</t>
+          <t>luke.king@hotmail.com</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>luke.king@hotmail.com</t>
+          <t>Parent</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Mr. Mark Vance</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Mr. Mark Vance</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
           <t>12/05/2023</t>
         </is>
       </c>
-      <c r="O108" t="n">
+      <c r="N108" t="n">
         <v>91</v>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>86.0%</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>86.0%</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7311,46 +6783,41 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Parent: Aiden Scott | Ph: 555-787-4654 | Email: aiden.scott@gmail.com</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
           <t xml:space="preserve">276 Cedar Ln </t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Aiden Scott</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Aiden Scott</t>
+          <t>+15557874654</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>+15557874654</t>
+          <t>aiden.scott@gmail.com</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>aiden.scott@gmail.com</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7373,62 +6840,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Henry Wilson, henry.wilson@outlook.com, 555-624-6427</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
           <t xml:space="preserve">702 Maple Rd </t>
         </is>
       </c>
-      <c r="G110" t="n">
+      <c r="F110" t="n">
         <v>5000</v>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Henry Wilson</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Henry Wilson</t>
+          <t>+15556246427</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>+15556246427</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
           <t>henry.wilson@outlook.com</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Dr. Aris Thorne</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Dr. Aris Thorne</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
           <t>11/23/2023</t>
         </is>
       </c>
-      <c r="O110" t="n">
+      <c r="N110" t="n">
         <v>95</v>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>76.0%</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
         <is>
           <t>301</t>
         </is>
@@ -7455,42 +6917,37 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Maria Martinez, Ph: 5550123456, maria.m@hotmail.com</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
           <t>321 Cedar Ln</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Maria Martinez</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Maria Martinez</t>
+          <t>+15550123456</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>+15550123456</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
           <t>maria.m@hotmail.com</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7513,44 +6970,39 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Theodore Johnson (Parent) - 555-142-8542</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
           <t xml:space="preserve">797 Cedar Ln </t>
         </is>
       </c>
-      <c r="G112" t="n">
+      <c r="F112" t="n">
         <v>4500</v>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Theodore Johnson</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Theodore Johnson</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
           <t>+15551428542</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7573,44 +7025,39 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mother: Mary / 555-999-0000</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G113" t="n">
+      <c r="F113" t="n">
         <v>4500</v>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Mary</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
           <t>+15559990000</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7633,62 +7080,57 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Elijah Brown, elijah.brown@yahoo.com, 555-151-7755</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
           <t xml:space="preserve">452 Main St </t>
         </is>
       </c>
-      <c r="G114" t="n">
+      <c r="F114" t="n">
         <v>5000</v>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Elijah Brown</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Elijah Brown</t>
+          <t>+15551517755</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>+15551517755</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
           <t>elijah.brown@yahoo.com</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Mrs. Elena Rostova</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Mrs. Elena Rostova</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
           <t>10/17/2023</t>
         </is>
       </c>
-      <c r="O114" t="n">
+      <c r="N114" t="n">
         <v>64</v>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>History</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -7715,46 +7157,41 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mother: James Perez | Ph: 555-555-9740 | Email: james.perez@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
           <t xml:space="preserve">101 Cedar Ln </t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>James Perez</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>James Perez</t>
+          <t>+15555559740</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>+15555559740</t>
+          <t>james.perez@yahoo.com</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>james.perez@yahoo.com</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
           <t>Mother</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7777,44 +7214,39 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Father: Thomas Turner (555-013-4455)</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
           <t>159 Walnut St</t>
         </is>
       </c>
-      <c r="G116" t="n">
+      <c r="F116" t="n">
         <v>5000</v>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Graduating</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Graduating</t>
+          <t>Thomas Turner</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Thomas Turner</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
           <t>+15550134455</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7837,44 +7269,39 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Contact: 555-918-4197 / gabriel.lopez@outlook.com</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
           <t xml:space="preserve">446 Pine St </t>
         </is>
       </c>
-      <c r="G117" t="n">
+      <c r="F117" t="n">
         <v>4800</v>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Unknown Parent</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Unknown Parent</t>
+          <t>+15559184197</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>+15559184197</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
           <t>gabriel.lopez@outlook.com</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7897,44 +7324,39 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Henry Young, henry.young@yahoo.com, 555-267-9594</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
           <t xml:space="preserve">663 Main St </t>
         </is>
       </c>
-      <c r="G118" t="n">
+      <c r="F118" t="n">
         <v>3750</v>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Enrolled</t>
+          <t>Henry Young</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Henry Young</t>
+          <t>+15552679594</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>+15552679594</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
           <t>henry.young@yahoo.com</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
